--- a/data/employees/EMP011/AST-EMP011-06.xlsx
+++ b/data/employees/EMP011/AST-EMP011-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Alex Garcia (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Alex Garcia | Role: Lead | Location: Portland | Date: 2025-01-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>96</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>99</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>62</v>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>96</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>83</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>63</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>79</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>79</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>91</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>76</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>85</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp011 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>71</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP011</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP011 contributes to ast emp011 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>